--- a/templates/reports/수질분석일지.xlsx
+++ b/templates/reports/수질분석일지.xlsx
@@ -1,46 +1,205 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <workbookPr codeName="현재_통합_문서"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ASUS\OneDrive\바탕 화면\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E1062FF-32F0-4331-B237-5D2E8F893C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="28680" yWindow="-5970" windowWidth="29040" windowHeight="15720" xr2:uid="{E04081F6-BED5-43C5-8953-C8C5EE4CD292}"/>
+  </bookViews>
   <sheets>
-    <sheet sheetId="1" name="템플릿" state="visible" r:id="rId4"/>
+    <sheet name="01" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <definedNames>
+    <definedName name="LastRunMonth">202510</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'01'!$A$1:$Y$55</definedName>
+    <definedName name="_xlnm.Print_Area">#REF!,#REF!</definedName>
+    <definedName name="날짜">'01'!$U$2</definedName>
+    <definedName name="알칼리1">'01'!$F$54</definedName>
+    <definedName name="알칼리2">'01'!$I$54</definedName>
+    <definedName name="알칼리3">'01'!$L$54</definedName>
+    <definedName name="알칼리4">'01'!$O$54</definedName>
+    <definedName name="알칼리5">'01'!$R$54</definedName>
+    <definedName name="알칼리사진">'01'!$H$43</definedName>
+    <definedName name="암모니아1">'01'!$F$15</definedName>
+    <definedName name="암모니아2">'01'!$I$15</definedName>
+    <definedName name="암모니아3">'01'!$L$15</definedName>
+    <definedName name="암모니아4">'01'!$O$15</definedName>
+    <definedName name="암모니아5">'01'!$R$15</definedName>
+    <definedName name="암모니아사진">'01'!$H$4</definedName>
+    <definedName name="인1">'01'!$F$41</definedName>
+    <definedName name="인2">'01'!$K$41</definedName>
+    <definedName name="인3">'01'!$P$41</definedName>
+    <definedName name="인사진">'01'!$H$30</definedName>
+    <definedName name="질산1">'01'!$F$28</definedName>
+    <definedName name="질산2">'01'!$I$28</definedName>
+    <definedName name="질산3">'01'!$L$28</definedName>
+    <definedName name="질산4">'01'!$O$28</definedName>
+    <definedName name="질산5">'01'!$R$28</definedName>
+    <definedName name="질산사진">'01'!$H$17</definedName>
+  </definedNames>
+  <calcPr calcId="191029" iterateDelta="0"/>
+  <extLst>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
+      <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2" uniqueCount="2">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="10">
   <si>
-    <t>수질분석일지 기본 템플릿</t>
+    <t>비 고</t>
   </si>
   <si>
-    <t>이 파일은 기본 번들 템플릿입니다. 실제 양식은 필요에 따라 교체해주세요.</t>
+    <t>구    분</t>
+  </si>
+  <si>
+    <t>유량조정조/혐기조/ 무산소조/ 포기조/ 침전조/ 응집침전조( 방류조)</t>
+  </si>
+  <si>
+    <t>NH₃-N(질산화)</t>
+  </si>
+  <si>
+    <t>기준치 20ppm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>NO₃ -N(탈질)</t>
+  </si>
+  <si>
+    <t>PO₄³ -P(인)</t>
+  </si>
+  <si>
+    <t>기준치 2ppm</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>Alkalinity(알칼리도)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">        수질분석 일지</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="1" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="41" formatCode="_-* #,##0_-;\-* #,##0_-;_-* &quot;-&quot;_-;_-@_-"/>
+  </numFmts>
+  <fonts count="11">
     <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
       <sz val="11"/>
-      <name val="Calibri"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color rgb="FF000000"/>
+      <name val="휴먼명조"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="36"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FF000000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="36"/>
+      <color rgb="FFFF0000"/>
+      <name val="돋움"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="10">
     <border>
       <left/>
       <right/>
@@ -48,15 +207,230 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="4">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="37">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="4" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="6" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  <cellStyles count="4">
+    <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="표준 2 2" xfId="2" xr:uid="{D2ED8BDA-BD97-483C-9C6E-E195EDEA7997}"/>
+    <cellStyle name="표준 2 2 3" xfId="3" xr:uid="{78530279-EE2D-4A4F-92D0-4CEB9D0F6499}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -71,8 +445,106 @@
 </styleSheet>
 </file>
 
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>77</xdr:col>
+      <xdr:colOff>280147</xdr:colOff>
+      <xdr:row>0</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>82</xdr:col>
+      <xdr:colOff>53788</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>134027</xdr:rowOff>
+    </xdr:to>
+    <xdr:grpSp>
+      <xdr:nvGrpSpPr>
+        <xdr:cNvPr id="33" name="그룹 32">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{24A6B82C-2645-4F4C-B467-48A7CC239A98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGrpSpPr/>
+      </xdr:nvGrpSpPr>
+      <xdr:grpSpPr>
+        <a:xfrm>
+          <a:off x="46709928" y="0"/>
+          <a:ext cx="3191435" cy="4209158"/>
+          <a:chOff x="47075912" y="10363200"/>
+          <a:chExt cx="3191435" cy="6635680"/>
+        </a:xfrm>
+      </xdr:grpSpPr>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="34" name="그림 70" descr="20180508_180206.jpg">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8AC5C738-3BB9-3782-2BA0-D97AB4ADE69E}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="47366366" y="14097898"/>
+            <a:ext cx="3294086" cy="2507877"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+      <xdr:pic>
+        <xdr:nvPicPr>
+          <xdr:cNvPr id="35" name="그림 70" descr="20180508_180206.jpg">
+            <a:extLst>
+              <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+                <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4994FA60-4AA4-A58D-32A6-684C18AE75F5}"/>
+              </a:ext>
+            </a:extLst>
+          </xdr:cNvPr>
+          <xdr:cNvPicPr>
+            <a:picLocks noChangeAspect="1"/>
+          </xdr:cNvPicPr>
+        </xdr:nvPicPr>
+        <xdr:blipFill rotWithShape="1">
+          <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+          <a:stretch>
+            <a:fillRect/>
+          </a:stretch>
+        </xdr:blipFill>
+        <xdr:spPr>
+          <a:xfrm rot="5400000">
+            <a:off x="46704372" y="10734740"/>
+            <a:ext cx="3274904" cy="2531823"/>
+          </a:xfrm>
+          <a:prstGeom prst="rect">
+            <a:avLst/>
+          </a:prstGeom>
+        </xdr:spPr>
+      </xdr:pic>
+    </xdr:grpSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 테마">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -216,16 +688,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -282,17 +758,6 @@
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
@@ -347,67 +812,1600 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:A2"/>
-  <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{90277045-0D0C-48F8-8EF0-53D5A56CD128}">
+  <sheetPr codeName="Sheet11">
+    <tabColor rgb="FF00B050"/>
+  </sheetPr>
+  <dimension ref="A1:AI56"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="17.399999999999999"/>
+  <cols>
+    <col min="1" max="2" width="3.69921875" customWidth="1"/>
+    <col min="3" max="4" width="4.59765625" customWidth="1"/>
+    <col min="5" max="5" width="3.69921875" customWidth="1"/>
+    <col min="6" max="20" width="4.19921875" customWidth="1"/>
+    <col min="21" max="27" width="3.69921875" customWidth="1"/>
+    <col min="28" max="28" width="22.19921875" bestFit="1" customWidth="1"/>
+    <col min="35" max="40" width="15" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
+    <row r="1" spans="1:25" ht="55.2" customHeight="1">
+      <c r="A1" s="23" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1" s="23"/>
+      <c r="C1" s="23"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
+      <c r="M1" s="23"/>
+      <c r="N1" s="23"/>
+      <c r="O1" s="23"/>
+      <c r="P1" s="23"/>
+      <c r="Q1" s="23"/>
+      <c r="R1" s="23"/>
+      <c r="S1" s="23"/>
+      <c r="T1" s="23"/>
+    </row>
+    <row r="2" spans="1:25" ht="31.8" customHeight="1">
+      <c r="A2" s="24"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="10"/>
+      <c r="V2" s="10"/>
+      <c r="W2" s="10"/>
+      <c r="X2" s="10"/>
+      <c r="Y2" s="10"/>
+    </row>
+    <row r="3" spans="1:25" ht="32.1" customHeight="1">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11"/>
+      <c r="D3" s="11"/>
+      <c r="E3" s="11"/>
+      <c r="F3" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="11"/>
+      <c r="H3" s="11"/>
+      <c r="I3" s="11"/>
+      <c r="J3" s="11"/>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
+      <c r="N3" s="11"/>
+      <c r="O3" s="11"/>
+      <c r="P3" s="11"/>
+      <c r="Q3" s="11"/>
+      <c r="R3" s="11"/>
+      <c r="S3" s="11"/>
+      <c r="T3" s="11"/>
+      <c r="U3" s="11" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>1</v>
+      <c r="V3" s="11"/>
+      <c r="W3" s="11"/>
+      <c r="X3" s="11"/>
+      <c r="Y3" s="11"/>
+    </row>
+    <row r="4" spans="1:25">
+      <c r="A4" s="11" t="s">
+        <v>3</v>
       </c>
+      <c r="B4" s="11"/>
+      <c r="C4" s="11"/>
+      <c r="D4" s="11"/>
+      <c r="E4" s="11"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="31"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="31"/>
+      <c r="N4" s="31"/>
+      <c r="O4" s="31"/>
+      <c r="P4" s="31"/>
+      <c r="Q4" s="31"/>
+      <c r="R4" s="31"/>
+      <c r="S4" s="5"/>
+      <c r="T4" s="6"/>
+      <c r="U4" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="V4" s="12"/>
+      <c r="W4" s="12"/>
+      <c r="X4" s="12"/>
+      <c r="Y4" s="16"/>
+    </row>
+    <row r="5" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A5" s="11"/>
+      <c r="B5" s="11"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="11"/>
+      <c r="E5" s="11"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="32"/>
+      <c r="I5" s="32"/>
+      <c r="J5" s="32"/>
+      <c r="K5" s="32"/>
+      <c r="L5" s="32"/>
+      <c r="M5" s="32"/>
+      <c r="N5" s="32"/>
+      <c r="O5" s="32"/>
+      <c r="P5" s="32"/>
+      <c r="Q5" s="32"/>
+      <c r="R5" s="32"/>
+      <c r="S5" s="8"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="17"/>
+      <c r="V5" s="13"/>
+      <c r="W5" s="13"/>
+      <c r="X5" s="13"/>
+      <c r="Y5" s="18"/>
+    </row>
+    <row r="6" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A6" s="11"/>
+      <c r="B6" s="11"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="32"/>
+      <c r="I6" s="32"/>
+      <c r="J6" s="32"/>
+      <c r="K6" s="32"/>
+      <c r="L6" s="32"/>
+      <c r="M6" s="32"/>
+      <c r="N6" s="32"/>
+      <c r="O6" s="32"/>
+      <c r="P6" s="32"/>
+      <c r="Q6" s="32"/>
+      <c r="R6" s="32"/>
+      <c r="S6" s="8"/>
+      <c r="T6" s="9"/>
+      <c r="U6" s="17"/>
+      <c r="V6" s="13"/>
+      <c r="W6" s="13"/>
+      <c r="X6" s="13"/>
+      <c r="Y6" s="18"/>
+    </row>
+    <row r="7" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A7" s="11"/>
+      <c r="B7" s="11"/>
+      <c r="C7" s="11"/>
+      <c r="D7" s="11"/>
+      <c r="E7" s="11"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="8"/>
+      <c r="H7" s="32"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="32"/>
+      <c r="K7" s="32"/>
+      <c r="L7" s="32"/>
+      <c r="M7" s="32"/>
+      <c r="N7" s="32"/>
+      <c r="O7" s="32"/>
+      <c r="P7" s="32"/>
+      <c r="Q7" s="32"/>
+      <c r="R7" s="32"/>
+      <c r="S7" s="8"/>
+      <c r="T7" s="9"/>
+      <c r="U7" s="17"/>
+      <c r="V7" s="13"/>
+      <c r="W7" s="13"/>
+      <c r="X7" s="13"/>
+      <c r="Y7" s="18"/>
+    </row>
+    <row r="8" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A8" s="11"/>
+      <c r="B8" s="11"/>
+      <c r="C8" s="11"/>
+      <c r="D8" s="11"/>
+      <c r="E8" s="11"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="32"/>
+      <c r="I8" s="32"/>
+      <c r="J8" s="32"/>
+      <c r="K8" s="32"/>
+      <c r="L8" s="32"/>
+      <c r="M8" s="32"/>
+      <c r="N8" s="32"/>
+      <c r="O8" s="32"/>
+      <c r="P8" s="32"/>
+      <c r="Q8" s="32"/>
+      <c r="R8" s="32"/>
+      <c r="S8" s="8"/>
+      <c r="T8" s="9"/>
+      <c r="U8" s="17"/>
+      <c r="V8" s="13"/>
+      <c r="W8" s="13"/>
+      <c r="X8" s="13"/>
+      <c r="Y8" s="18"/>
+    </row>
+    <row r="9" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A9" s="11"/>
+      <c r="B9" s="11"/>
+      <c r="C9" s="11"/>
+      <c r="D9" s="11"/>
+      <c r="E9" s="11"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="32"/>
+      <c r="I9" s="32"/>
+      <c r="J9" s="32"/>
+      <c r="K9" s="32"/>
+      <c r="L9" s="32"/>
+      <c r="M9" s="32"/>
+      <c r="N9" s="32"/>
+      <c r="O9" s="32"/>
+      <c r="P9" s="32"/>
+      <c r="Q9" s="32"/>
+      <c r="R9" s="32"/>
+      <c r="S9" s="8"/>
+      <c r="T9" s="9"/>
+      <c r="U9" s="17"/>
+      <c r="V9" s="13"/>
+      <c r="W9" s="13"/>
+      <c r="X9" s="13"/>
+      <c r="Y9" s="18"/>
+    </row>
+    <row r="10" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A10" s="11"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="11"/>
+      <c r="D10" s="11"/>
+      <c r="E10" s="11"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="32"/>
+      <c r="I10" s="32"/>
+      <c r="J10" s="32"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
+      <c r="N10" s="32"/>
+      <c r="O10" s="32"/>
+      <c r="P10" s="32"/>
+      <c r="Q10" s="32"/>
+      <c r="R10" s="32"/>
+      <c r="S10" s="8"/>
+      <c r="T10" s="9"/>
+      <c r="U10" s="17"/>
+      <c r="V10" s="13"/>
+      <c r="W10" s="13"/>
+      <c r="X10" s="13"/>
+      <c r="Y10" s="18"/>
+    </row>
+    <row r="11" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A11" s="11"/>
+      <c r="B11" s="11"/>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="32"/>
+      <c r="J11" s="32"/>
+      <c r="K11" s="32"/>
+      <c r="L11" s="32"/>
+      <c r="M11" s="32"/>
+      <c r="N11" s="32"/>
+      <c r="O11" s="32"/>
+      <c r="P11" s="32"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="8"/>
+      <c r="T11" s="9"/>
+      <c r="U11" s="17"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="18"/>
+    </row>
+    <row r="12" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A12" s="11"/>
+      <c r="B12" s="11"/>
+      <c r="C12" s="11"/>
+      <c r="D12" s="11"/>
+      <c r="E12" s="11"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="8"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="32"/>
+      <c r="J12" s="32"/>
+      <c r="K12" s="32"/>
+      <c r="L12" s="32"/>
+      <c r="M12" s="32"/>
+      <c r="N12" s="32"/>
+      <c r="O12" s="32"/>
+      <c r="P12" s="32"/>
+      <c r="Q12" s="32"/>
+      <c r="R12" s="32"/>
+      <c r="S12" s="8"/>
+      <c r="T12" s="9"/>
+      <c r="U12" s="17"/>
+      <c r="V12" s="13"/>
+      <c r="W12" s="13"/>
+      <c r="X12" s="13"/>
+      <c r="Y12" s="18"/>
+    </row>
+    <row r="13" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A13" s="11"/>
+      <c r="B13" s="11"/>
+      <c r="C13" s="11"/>
+      <c r="D13" s="11"/>
+      <c r="E13" s="11"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="8"/>
+      <c r="H13" s="32"/>
+      <c r="I13" s="32"/>
+      <c r="J13" s="32"/>
+      <c r="K13" s="32"/>
+      <c r="L13" s="32"/>
+      <c r="M13" s="32"/>
+      <c r="N13" s="32"/>
+      <c r="O13" s="32"/>
+      <c r="P13" s="32"/>
+      <c r="Q13" s="32"/>
+      <c r="R13" s="32"/>
+      <c r="S13" s="8"/>
+      <c r="T13" s="9"/>
+      <c r="U13" s="17"/>
+      <c r="V13" s="13"/>
+      <c r="W13" s="13"/>
+      <c r="X13" s="13"/>
+      <c r="Y13" s="18"/>
+    </row>
+    <row r="14" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A14" s="11"/>
+      <c r="B14" s="11"/>
+      <c r="C14" s="11"/>
+      <c r="D14" s="11"/>
+      <c r="E14" s="11"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="8"/>
+      <c r="H14" s="33"/>
+      <c r="I14" s="33"/>
+      <c r="J14" s="33"/>
+      <c r="K14" s="33"/>
+      <c r="L14" s="33"/>
+      <c r="M14" s="33"/>
+      <c r="N14" s="33"/>
+      <c r="O14" s="33"/>
+      <c r="P14" s="33"/>
+      <c r="Q14" s="33"/>
+      <c r="R14" s="33"/>
+      <c r="S14" s="8"/>
+      <c r="T14" s="9"/>
+      <c r="U14" s="17"/>
+      <c r="V14" s="13"/>
+      <c r="W14" s="13"/>
+      <c r="X14" s="13"/>
+      <c r="Y14" s="18"/>
+    </row>
+    <row r="15" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A15" s="11"/>
+      <c r="B15" s="11"/>
+      <c r="C15" s="11"/>
+      <c r="D15" s="11"/>
+      <c r="E15" s="11"/>
+      <c r="F15" s="21"/>
+      <c r="G15" s="21"/>
+      <c r="H15" s="21"/>
+      <c r="I15" s="21"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="21"/>
+      <c r="L15" s="21"/>
+      <c r="M15" s="21"/>
+      <c r="N15" s="21"/>
+      <c r="O15" s="21"/>
+      <c r="P15" s="21"/>
+      <c r="Q15" s="21"/>
+      <c r="R15" s="22"/>
+      <c r="S15" s="22"/>
+      <c r="T15" s="22"/>
+      <c r="U15" s="17"/>
+      <c r="V15" s="13"/>
+      <c r="W15" s="13"/>
+      <c r="X15" s="13"/>
+      <c r="Y15" s="18"/>
+    </row>
+    <row r="16" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A16" s="11"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="11"/>
+      <c r="D16" s="11"/>
+      <c r="E16" s="11"/>
+      <c r="F16" s="21"/>
+      <c r="G16" s="21"/>
+      <c r="H16" s="21"/>
+      <c r="I16" s="21"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="21"/>
+      <c r="L16" s="21"/>
+      <c r="M16" s="21"/>
+      <c r="N16" s="21"/>
+      <c r="O16" s="21"/>
+      <c r="P16" s="21"/>
+      <c r="Q16" s="21"/>
+      <c r="R16" s="22"/>
+      <c r="S16" s="22"/>
+      <c r="T16" s="22"/>
+      <c r="U16" s="19"/>
+      <c r="V16" s="14"/>
+      <c r="W16" s="14"/>
+      <c r="X16" s="14"/>
+      <c r="Y16" s="20"/>
+    </row>
+    <row r="17" spans="1:25">
+      <c r="A17" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="16"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="5"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="34"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="5"/>
+      <c r="T17" s="6"/>
+      <c r="U17" s="15" t="s">
+        <v>4</v>
+      </c>
+      <c r="V17" s="12"/>
+      <c r="W17" s="12"/>
+      <c r="X17" s="12"/>
+      <c r="Y17" s="16"/>
+    </row>
+    <row r="18" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A18" s="17"/>
+      <c r="B18" s="13"/>
+      <c r="C18" s="13"/>
+      <c r="D18" s="13"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="8"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="35"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="8"/>
+      <c r="T18" s="9"/>
+      <c r="U18" s="17"/>
+      <c r="V18" s="13"/>
+      <c r="W18" s="13"/>
+      <c r="X18" s="13"/>
+      <c r="Y18" s="18"/>
+    </row>
+    <row r="19" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A19" s="17"/>
+      <c r="B19" s="13"/>
+      <c r="C19" s="13"/>
+      <c r="D19" s="13"/>
+      <c r="E19" s="18"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="35"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="8"/>
+      <c r="T19" s="9"/>
+      <c r="U19" s="17"/>
+      <c r="V19" s="13"/>
+      <c r="W19" s="13"/>
+      <c r="X19" s="13"/>
+      <c r="Y19" s="18"/>
+    </row>
+    <row r="20" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A20" s="17"/>
+      <c r="B20" s="13"/>
+      <c r="C20" s="13"/>
+      <c r="D20" s="13"/>
+      <c r="E20" s="18"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="8"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="35"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="8"/>
+      <c r="T20" s="9"/>
+      <c r="U20" s="17"/>
+      <c r="V20" s="13"/>
+      <c r="W20" s="13"/>
+      <c r="X20" s="13"/>
+      <c r="Y20" s="18"/>
+    </row>
+    <row r="21" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A21" s="17"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="18"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="8"/>
+      <c r="H21" s="35"/>
+      <c r="I21" s="35"/>
+      <c r="J21" s="35"/>
+      <c r="K21" s="35"/>
+      <c r="L21" s="35"/>
+      <c r="M21" s="35"/>
+      <c r="N21" s="35"/>
+      <c r="O21" s="35"/>
+      <c r="P21" s="35"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="8"/>
+      <c r="T21" s="9"/>
+      <c r="U21" s="17"/>
+      <c r="V21" s="13"/>
+      <c r="W21" s="13"/>
+      <c r="X21" s="13"/>
+      <c r="Y21" s="18"/>
+    </row>
+    <row r="22" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A22" s="17"/>
+      <c r="B22" s="13"/>
+      <c r="C22" s="13"/>
+      <c r="D22" s="13"/>
+      <c r="E22" s="18"/>
+      <c r="F22" s="7"/>
+      <c r="G22" s="8"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="8"/>
+      <c r="T22" s="9"/>
+      <c r="U22" s="17"/>
+      <c r="V22" s="13"/>
+      <c r="W22" s="13"/>
+      <c r="X22" s="13"/>
+      <c r="Y22" s="18"/>
+    </row>
+    <row r="23" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A23" s="17"/>
+      <c r="B23" s="13"/>
+      <c r="C23" s="13"/>
+      <c r="D23" s="13"/>
+      <c r="E23" s="18"/>
+      <c r="F23" s="7"/>
+      <c r="G23" s="8"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="8"/>
+      <c r="T23" s="9"/>
+      <c r="U23" s="17"/>
+      <c r="V23" s="13"/>
+      <c r="W23" s="13"/>
+      <c r="X23" s="13"/>
+      <c r="Y23" s="18"/>
+    </row>
+    <row r="24" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A24" s="17"/>
+      <c r="B24" s="13"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="18"/>
+      <c r="F24" s="7"/>
+      <c r="G24" s="8"/>
+      <c r="H24" s="35"/>
+      <c r="I24" s="35"/>
+      <c r="J24" s="35"/>
+      <c r="K24" s="35"/>
+      <c r="L24" s="35"/>
+      <c r="M24" s="35"/>
+      <c r="N24" s="35"/>
+      <c r="O24" s="35"/>
+      <c r="P24" s="35"/>
+      <c r="Q24" s="35"/>
+      <c r="R24" s="35"/>
+      <c r="S24" s="8"/>
+      <c r="T24" s="9"/>
+      <c r="U24" s="17"/>
+      <c r="V24" s="13"/>
+      <c r="W24" s="13"/>
+      <c r="X24" s="13"/>
+      <c r="Y24" s="18"/>
+    </row>
+    <row r="25" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A25" s="17"/>
+      <c r="B25" s="13"/>
+      <c r="C25" s="13"/>
+      <c r="D25" s="13"/>
+      <c r="E25" s="18"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="8"/>
+      <c r="H25" s="35"/>
+      <c r="I25" s="35"/>
+      <c r="J25" s="35"/>
+      <c r="K25" s="35"/>
+      <c r="L25" s="35"/>
+      <c r="M25" s="35"/>
+      <c r="N25" s="35"/>
+      <c r="O25" s="35"/>
+      <c r="P25" s="35"/>
+      <c r="Q25" s="35"/>
+      <c r="R25" s="35"/>
+      <c r="S25" s="8"/>
+      <c r="T25" s="9"/>
+      <c r="U25" s="17"/>
+      <c r="V25" s="13"/>
+      <c r="W25" s="13"/>
+      <c r="X25" s="13"/>
+      <c r="Y25" s="18"/>
+    </row>
+    <row r="26" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A26" s="17"/>
+      <c r="B26" s="13"/>
+      <c r="C26" s="13"/>
+      <c r="D26" s="13"/>
+      <c r="E26" s="18"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="8"/>
+      <c r="H26" s="35"/>
+      <c r="I26" s="35"/>
+      <c r="J26" s="35"/>
+      <c r="K26" s="35"/>
+      <c r="L26" s="35"/>
+      <c r="M26" s="35"/>
+      <c r="N26" s="35"/>
+      <c r="O26" s="35"/>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="35"/>
+      <c r="R26" s="35"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="9"/>
+      <c r="U26" s="17"/>
+      <c r="V26" s="13"/>
+      <c r="W26" s="13"/>
+      <c r="X26" s="13"/>
+      <c r="Y26" s="18"/>
+    </row>
+    <row r="27" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A27" s="17"/>
+      <c r="B27" s="13"/>
+      <c r="C27" s="13"/>
+      <c r="D27" s="13"/>
+      <c r="E27" s="18"/>
+      <c r="F27" s="7"/>
+      <c r="G27" s="8"/>
+      <c r="H27" s="36"/>
+      <c r="I27" s="36"/>
+      <c r="J27" s="36"/>
+      <c r="K27" s="36"/>
+      <c r="L27" s="36"/>
+      <c r="M27" s="36"/>
+      <c r="N27" s="36"/>
+      <c r="O27" s="36"/>
+      <c r="P27" s="36"/>
+      <c r="Q27" s="36"/>
+      <c r="R27" s="36"/>
+      <c r="S27" s="8"/>
+      <c r="T27" s="9"/>
+      <c r="U27" s="17"/>
+      <c r="V27" s="13"/>
+      <c r="W27" s="13"/>
+      <c r="X27" s="13"/>
+      <c r="Y27" s="18"/>
+    </row>
+    <row r="28" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A28" s="17"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="13"/>
+      <c r="D28" s="13"/>
+      <c r="E28" s="18"/>
+      <c r="F28" s="21"/>
+      <c r="G28" s="21"/>
+      <c r="H28" s="21"/>
+      <c r="I28" s="21"/>
+      <c r="J28" s="21"/>
+      <c r="K28" s="21"/>
+      <c r="L28" s="21"/>
+      <c r="M28" s="21"/>
+      <c r="N28" s="21"/>
+      <c r="O28" s="21"/>
+      <c r="P28" s="21"/>
+      <c r="Q28" s="21"/>
+      <c r="R28" s="21"/>
+      <c r="S28" s="21"/>
+      <c r="T28" s="21"/>
+      <c r="U28" s="17"/>
+      <c r="V28" s="13"/>
+      <c r="W28" s="13"/>
+      <c r="X28" s="13"/>
+      <c r="Y28" s="18"/>
+    </row>
+    <row r="29" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A29" s="17"/>
+      <c r="B29" s="13"/>
+      <c r="C29" s="13"/>
+      <c r="D29" s="13"/>
+      <c r="E29" s="18"/>
+      <c r="F29" s="21"/>
+      <c r="G29" s="21"/>
+      <c r="H29" s="21"/>
+      <c r="I29" s="21"/>
+      <c r="J29" s="21"/>
+      <c r="K29" s="21"/>
+      <c r="L29" s="21"/>
+      <c r="M29" s="21"/>
+      <c r="N29" s="21"/>
+      <c r="O29" s="21"/>
+      <c r="P29" s="21"/>
+      <c r="Q29" s="21"/>
+      <c r="R29" s="21"/>
+      <c r="S29" s="21"/>
+      <c r="T29" s="21"/>
+      <c r="U29" s="19"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="20"/>
+    </row>
+    <row r="30" spans="1:25">
+      <c r="A30" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="16"/>
+      <c r="F30" s="4"/>
+      <c r="G30" s="5"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="34"/>
+      <c r="N30" s="34"/>
+      <c r="O30" s="34"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="34"/>
+      <c r="R30" s="34"/>
+      <c r="S30" s="5"/>
+      <c r="T30" s="6"/>
+      <c r="U30" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="16"/>
+    </row>
+    <row r="31" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A31" s="17"/>
+      <c r="B31" s="13"/>
+      <c r="C31" s="13"/>
+      <c r="D31" s="13"/>
+      <c r="E31" s="18"/>
+      <c r="F31" s="7"/>
+      <c r="G31" s="8"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="35"/>
+      <c r="N31" s="35"/>
+      <c r="O31" s="35"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="35"/>
+      <c r="R31" s="35"/>
+      <c r="S31" s="8"/>
+      <c r="T31" s="9"/>
+      <c r="U31" s="17"/>
+      <c r="V31" s="13"/>
+      <c r="W31" s="13"/>
+      <c r="X31" s="13"/>
+      <c r="Y31" s="18"/>
+    </row>
+    <row r="32" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A32" s="17"/>
+      <c r="B32" s="13"/>
+      <c r="C32" s="13"/>
+      <c r="D32" s="13"/>
+      <c r="E32" s="18"/>
+      <c r="F32" s="7"/>
+      <c r="G32" s="8"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="8"/>
+      <c r="T32" s="9"/>
+      <c r="U32" s="17"/>
+      <c r="V32" s="13"/>
+      <c r="W32" s="13"/>
+      <c r="X32" s="13"/>
+      <c r="Y32" s="18"/>
+    </row>
+    <row r="33" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A33" s="17"/>
+      <c r="B33" s="13"/>
+      <c r="C33" s="13"/>
+      <c r="D33" s="13"/>
+      <c r="E33" s="18"/>
+      <c r="F33" s="7"/>
+      <c r="G33" s="8"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="8"/>
+      <c r="T33" s="9"/>
+      <c r="U33" s="17"/>
+      <c r="V33" s="13"/>
+      <c r="W33" s="13"/>
+      <c r="X33" s="13"/>
+      <c r="Y33" s="18"/>
+    </row>
+    <row r="34" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A34" s="17"/>
+      <c r="B34" s="13"/>
+      <c r="C34" s="13"/>
+      <c r="D34" s="13"/>
+      <c r="E34" s="18"/>
+      <c r="F34" s="7"/>
+      <c r="G34" s="8"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="8"/>
+      <c r="T34" s="9"/>
+      <c r="U34" s="17"/>
+      <c r="V34" s="13"/>
+      <c r="W34" s="13"/>
+      <c r="X34" s="13"/>
+      <c r="Y34" s="18"/>
+    </row>
+    <row r="35" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A35" s="17"/>
+      <c r="B35" s="13"/>
+      <c r="C35" s="13"/>
+      <c r="D35" s="13"/>
+      <c r="E35" s="18"/>
+      <c r="F35" s="7"/>
+      <c r="G35" s="8"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="8"/>
+      <c r="T35" s="9"/>
+      <c r="U35" s="17"/>
+      <c r="V35" s="13"/>
+      <c r="W35" s="13"/>
+      <c r="X35" s="13"/>
+      <c r="Y35" s="18"/>
+    </row>
+    <row r="36" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A36" s="17"/>
+      <c r="B36" s="13"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="18"/>
+      <c r="F36" s="7"/>
+      <c r="G36" s="8"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="8"/>
+      <c r="T36" s="9"/>
+      <c r="U36" s="17"/>
+      <c r="V36" s="13"/>
+      <c r="W36" s="13"/>
+      <c r="X36" s="13"/>
+      <c r="Y36" s="18"/>
+    </row>
+    <row r="37" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A37" s="17"/>
+      <c r="B37" s="13"/>
+      <c r="C37" s="13"/>
+      <c r="D37" s="13"/>
+      <c r="E37" s="18"/>
+      <c r="F37" s="7"/>
+      <c r="G37" s="8"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="8"/>
+      <c r="T37" s="9"/>
+      <c r="U37" s="17"/>
+      <c r="V37" s="13"/>
+      <c r="W37" s="13"/>
+      <c r="X37" s="13"/>
+      <c r="Y37" s="18"/>
+    </row>
+    <row r="38" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A38" s="17"/>
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="18"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="8"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="35"/>
+      <c r="K38" s="35"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="35"/>
+      <c r="N38" s="35"/>
+      <c r="O38" s="35"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="35"/>
+      <c r="R38" s="35"/>
+      <c r="S38" s="8"/>
+      <c r="T38" s="9"/>
+      <c r="U38" s="17"/>
+      <c r="V38" s="13"/>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
+      <c r="Y38" s="18"/>
+    </row>
+    <row r="39" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A39" s="17"/>
+      <c r="B39" s="13"/>
+      <c r="C39" s="13"/>
+      <c r="D39" s="13"/>
+      <c r="E39" s="18"/>
+      <c r="F39" s="7"/>
+      <c r="G39" s="8"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="8"/>
+      <c r="T39" s="9"/>
+      <c r="U39" s="17"/>
+      <c r="V39" s="13"/>
+      <c r="W39" s="13"/>
+      <c r="X39" s="13"/>
+      <c r="Y39" s="18"/>
+    </row>
+    <row r="40" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A40" s="17"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="13"/>
+      <c r="D40" s="13"/>
+      <c r="E40" s="18"/>
+      <c r="F40" s="7"/>
+      <c r="G40" s="8"/>
+      <c r="H40" s="36"/>
+      <c r="I40" s="36"/>
+      <c r="J40" s="36"/>
+      <c r="K40" s="36"/>
+      <c r="L40" s="36"/>
+      <c r="M40" s="36"/>
+      <c r="N40" s="36"/>
+      <c r="O40" s="36"/>
+      <c r="P40" s="36"/>
+      <c r="Q40" s="36"/>
+      <c r="R40" s="36"/>
+      <c r="S40" s="8"/>
+      <c r="T40" s="9"/>
+      <c r="U40" s="17"/>
+      <c r="V40" s="13"/>
+      <c r="W40" s="13"/>
+      <c r="X40" s="13"/>
+      <c r="Y40" s="18"/>
+    </row>
+    <row r="41" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A41" s="17"/>
+      <c r="B41" s="13"/>
+      <c r="C41" s="13"/>
+      <c r="D41" s="13"/>
+      <c r="E41" s="18"/>
+      <c r="F41" s="25"/>
+      <c r="G41" s="26"/>
+      <c r="H41" s="26"/>
+      <c r="I41" s="26"/>
+      <c r="J41" s="27"/>
+      <c r="K41" s="25"/>
+      <c r="L41" s="26"/>
+      <c r="M41" s="26"/>
+      <c r="N41" s="26"/>
+      <c r="O41" s="27"/>
+      <c r="P41" s="25"/>
+      <c r="Q41" s="26"/>
+      <c r="R41" s="26"/>
+      <c r="S41" s="26"/>
+      <c r="T41" s="27"/>
+      <c r="U41" s="17"/>
+      <c r="V41" s="13"/>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="18"/>
+    </row>
+    <row r="42" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A42" s="17"/>
+      <c r="B42" s="13"/>
+      <c r="C42" s="13"/>
+      <c r="D42" s="13"/>
+      <c r="E42" s="18"/>
+      <c r="F42" s="28"/>
+      <c r="G42" s="29"/>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29"/>
+      <c r="J42" s="30"/>
+      <c r="K42" s="28"/>
+      <c r="L42" s="29"/>
+      <c r="M42" s="29"/>
+      <c r="N42" s="29"/>
+      <c r="O42" s="30"/>
+      <c r="P42" s="28"/>
+      <c r="Q42" s="29"/>
+      <c r="R42" s="29"/>
+      <c r="S42" s="29"/>
+      <c r="T42" s="30"/>
+      <c r="U42" s="19"/>
+      <c r="V42" s="14"/>
+      <c r="W42" s="14"/>
+      <c r="X42" s="14"/>
+      <c r="Y42" s="20"/>
+    </row>
+    <row r="43" spans="1:25">
+      <c r="A43" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B43" s="11"/>
+      <c r="C43" s="11"/>
+      <c r="D43" s="11"/>
+      <c r="E43" s="11"/>
+      <c r="F43" s="4"/>
+      <c r="G43" s="5"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
+      <c r="M43" s="34"/>
+      <c r="N43" s="34"/>
+      <c r="O43" s="34"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="5"/>
+      <c r="T43" s="6"/>
+      <c r="U43" s="15"/>
+      <c r="V43" s="12"/>
+      <c r="W43" s="12"/>
+      <c r="X43" s="12"/>
+      <c r="Y43" s="16"/>
+    </row>
+    <row r="44" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A44" s="11"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="7"/>
+      <c r="G44" s="8"/>
+      <c r="H44" s="35"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="8"/>
+      <c r="T44" s="9"/>
+      <c r="U44" s="17"/>
+      <c r="V44" s="13"/>
+      <c r="W44" s="13"/>
+      <c r="X44" s="13"/>
+      <c r="Y44" s="18"/>
+    </row>
+    <row r="45" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A45" s="11"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="8"/>
+      <c r="H45" s="35"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
+      <c r="S45" s="8"/>
+      <c r="T45" s="9"/>
+      <c r="U45" s="17"/>
+      <c r="V45" s="13"/>
+      <c r="W45" s="13"/>
+      <c r="X45" s="13"/>
+      <c r="Y45" s="18"/>
+    </row>
+    <row r="46" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A46" s="11"/>
+      <c r="B46" s="11"/>
+      <c r="C46" s="11"/>
+      <c r="D46" s="11"/>
+      <c r="E46" s="11"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="8"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="8"/>
+      <c r="T46" s="9"/>
+      <c r="U46" s="17"/>
+      <c r="V46" s="13"/>
+      <c r="W46" s="13"/>
+      <c r="X46" s="13"/>
+      <c r="Y46" s="18"/>
+    </row>
+    <row r="47" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A47" s="11"/>
+      <c r="B47" s="11"/>
+      <c r="C47" s="11"/>
+      <c r="D47" s="11"/>
+      <c r="E47" s="11"/>
+      <c r="F47" s="7"/>
+      <c r="G47" s="8"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="8"/>
+      <c r="T47" s="9"/>
+      <c r="U47" s="17"/>
+      <c r="V47" s="13"/>
+      <c r="W47" s="13"/>
+      <c r="X47" s="13"/>
+      <c r="Y47" s="18"/>
+    </row>
+    <row r="48" spans="1:25" ht="16.5" customHeight="1">
+      <c r="A48" s="11"/>
+      <c r="B48" s="11"/>
+      <c r="C48" s="11"/>
+      <c r="D48" s="11"/>
+      <c r="E48" s="11"/>
+      <c r="F48" s="7"/>
+      <c r="G48" s="8"/>
+      <c r="H48" s="35"/>
+      <c r="I48" s="35"/>
+      <c r="J48" s="35"/>
+      <c r="K48" s="35"/>
+      <c r="L48" s="35"/>
+      <c r="M48" s="35"/>
+      <c r="N48" s="35"/>
+      <c r="O48" s="35"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="35"/>
+      <c r="R48" s="35"/>
+      <c r="S48" s="8"/>
+      <c r="T48" s="9"/>
+      <c r="U48" s="17"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13"/>
+      <c r="X48" s="13"/>
+      <c r="Y48" s="18"/>
+    </row>
+    <row r="49" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A49" s="11"/>
+      <c r="B49" s="11"/>
+      <c r="C49" s="11"/>
+      <c r="D49" s="11"/>
+      <c r="E49" s="11"/>
+      <c r="F49" s="7"/>
+      <c r="G49" s="8"/>
+      <c r="H49" s="35"/>
+      <c r="I49" s="35"/>
+      <c r="J49" s="35"/>
+      <c r="K49" s="35"/>
+      <c r="L49" s="35"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+      <c r="R49" s="35"/>
+      <c r="S49" s="8"/>
+      <c r="T49" s="9"/>
+      <c r="U49" s="17"/>
+      <c r="V49" s="13"/>
+      <c r="W49" s="13"/>
+      <c r="X49" s="13"/>
+      <c r="Y49" s="18"/>
+    </row>
+    <row r="50" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A50" s="11"/>
+      <c r="B50" s="11"/>
+      <c r="C50" s="11"/>
+      <c r="D50" s="11"/>
+      <c r="E50" s="11"/>
+      <c r="F50" s="7"/>
+      <c r="G50" s="8"/>
+      <c r="H50" s="35"/>
+      <c r="I50" s="35"/>
+      <c r="J50" s="35"/>
+      <c r="K50" s="35"/>
+      <c r="L50" s="35"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="8"/>
+      <c r="T50" s="9"/>
+      <c r="U50" s="17"/>
+      <c r="V50" s="13"/>
+      <c r="W50" s="13"/>
+      <c r="X50" s="13"/>
+      <c r="Y50" s="18"/>
+    </row>
+    <row r="51" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A51" s="11"/>
+      <c r="B51" s="11"/>
+      <c r="C51" s="11"/>
+      <c r="D51" s="11"/>
+      <c r="E51" s="11"/>
+      <c r="F51" s="7"/>
+      <c r="G51" s="8"/>
+      <c r="H51" s="35"/>
+      <c r="I51" s="35"/>
+      <c r="J51" s="35"/>
+      <c r="K51" s="35"/>
+      <c r="L51" s="35"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="35"/>
+      <c r="S51" s="8"/>
+      <c r="T51" s="9"/>
+      <c r="U51" s="17"/>
+      <c r="V51" s="13"/>
+      <c r="W51" s="13"/>
+      <c r="X51" s="13"/>
+      <c r="Y51" s="18"/>
+    </row>
+    <row r="52" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A52" s="11"/>
+      <c r="B52" s="11"/>
+      <c r="C52" s="11"/>
+      <c r="D52" s="11"/>
+      <c r="E52" s="11"/>
+      <c r="F52" s="7"/>
+      <c r="G52" s="8"/>
+      <c r="H52" s="35"/>
+      <c r="I52" s="35"/>
+      <c r="J52" s="35"/>
+      <c r="K52" s="35"/>
+      <c r="L52" s="35"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="8"/>
+      <c r="T52" s="9"/>
+      <c r="U52" s="17"/>
+      <c r="V52" s="13"/>
+      <c r="W52" s="13"/>
+      <c r="X52" s="13"/>
+      <c r="Y52" s="18"/>
+    </row>
+    <row r="53" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A53" s="11"/>
+      <c r="B53" s="11"/>
+      <c r="C53" s="11"/>
+      <c r="D53" s="11"/>
+      <c r="E53" s="11"/>
+      <c r="F53" s="7"/>
+      <c r="G53" s="8"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="36"/>
+      <c r="J53" s="36"/>
+      <c r="K53" s="36"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="36"/>
+      <c r="N53" s="36"/>
+      <c r="O53" s="36"/>
+      <c r="P53" s="36"/>
+      <c r="Q53" s="36"/>
+      <c r="R53" s="36"/>
+      <c r="S53" s="8"/>
+      <c r="T53" s="9"/>
+      <c r="U53" s="17"/>
+      <c r="V53" s="13"/>
+      <c r="W53" s="13"/>
+      <c r="X53" s="13"/>
+      <c r="Y53" s="18"/>
+    </row>
+    <row r="54" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A54" s="11"/>
+      <c r="B54" s="11"/>
+      <c r="C54" s="11"/>
+      <c r="D54" s="11"/>
+      <c r="E54" s="11"/>
+      <c r="F54" s="21"/>
+      <c r="G54" s="21"/>
+      <c r="H54" s="21"/>
+      <c r="I54" s="21"/>
+      <c r="J54" s="21"/>
+      <c r="K54" s="21"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+      <c r="P54" s="21"/>
+      <c r="Q54" s="21"/>
+      <c r="R54" s="21"/>
+      <c r="S54" s="21"/>
+      <c r="T54" s="21"/>
+      <c r="U54" s="17"/>
+      <c r="V54" s="13"/>
+      <c r="W54" s="13"/>
+      <c r="X54" s="13"/>
+      <c r="Y54" s="18"/>
+    </row>
+    <row r="55" spans="1:35" ht="16.5" customHeight="1">
+      <c r="A55" s="11"/>
+      <c r="B55" s="11"/>
+      <c r="C55" s="11"/>
+      <c r="D55" s="11"/>
+      <c r="E55" s="11"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="21"/>
+      <c r="H55" s="21"/>
+      <c r="I55" s="21"/>
+      <c r="J55" s="21"/>
+      <c r="K55" s="21"/>
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+      <c r="P55" s="21"/>
+      <c r="Q55" s="21"/>
+      <c r="R55" s="21"/>
+      <c r="S55" s="21"/>
+      <c r="T55" s="21"/>
+      <c r="U55" s="19"/>
+      <c r="V55" s="14"/>
+      <c r="W55" s="14"/>
+      <c r="X55" s="14"/>
+      <c r="Y55" s="20"/>
+    </row>
+    <row r="56" spans="1:35" ht="25.95" customHeight="1">
+      <c r="A56" s="2"/>
+      <c r="B56" s="2"/>
+      <c r="C56" s="2"/>
+      <c r="D56" s="2"/>
+      <c r="E56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="H56" s="2"/>
+      <c r="I56" s="2"/>
+      <c r="J56" s="2"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="2"/>
+      <c r="M56" s="2"/>
+      <c r="N56" s="3"/>
+      <c r="O56" s="2"/>
+      <c r="P56" s="2"/>
+      <c r="Q56" s="3"/>
+      <c r="R56" s="2"/>
+      <c r="S56" s="2"/>
+      <c r="T56" s="2"/>
+      <c r="U56" s="2"/>
+      <c r="V56" s="2"/>
+      <c r="W56" s="2"/>
+      <c r="X56" s="2"/>
+      <c r="Y56" s="2"/>
+      <c r="AI56" s="1"/>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
+  <mergeCells count="35">
+    <mergeCell ref="A43:E55"/>
+    <mergeCell ref="A30:E42"/>
+    <mergeCell ref="A4:E16"/>
+    <mergeCell ref="U43:Y55"/>
+    <mergeCell ref="F54:H55"/>
+    <mergeCell ref="I54:K55"/>
+    <mergeCell ref="L54:N55"/>
+    <mergeCell ref="O54:Q55"/>
+    <mergeCell ref="R54:T55"/>
+    <mergeCell ref="H43:R53"/>
+    <mergeCell ref="U30:Y42"/>
+    <mergeCell ref="A17:E29"/>
+    <mergeCell ref="U17:Y29"/>
+    <mergeCell ref="F28:H29"/>
+    <mergeCell ref="I28:K29"/>
+    <mergeCell ref="L28:N29"/>
+    <mergeCell ref="O28:Q29"/>
+    <mergeCell ref="R28:T29"/>
+    <mergeCell ref="H17:R27"/>
+    <mergeCell ref="H30:R40"/>
+    <mergeCell ref="F41:J42"/>
+    <mergeCell ref="K41:O42"/>
+    <mergeCell ref="P41:T42"/>
+    <mergeCell ref="U2:Y2"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="F3:T3"/>
+    <mergeCell ref="U3:Y3"/>
+    <mergeCell ref="H4:R14"/>
+    <mergeCell ref="U4:Y16"/>
+    <mergeCell ref="F15:H16"/>
+    <mergeCell ref="I15:K16"/>
+    <mergeCell ref="L15:N16"/>
+    <mergeCell ref="O15:Q16"/>
+    <mergeCell ref="R15:T16"/>
+    <mergeCell ref="A1:T2"/>
+  </mergeCells>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <printOptions horizontalCentered="1" verticalCentered="1"/>
+  <pageMargins left="0.23622047244094491" right="0.31496062992125984" top="0.47244094488188981" bottom="0.47244094488188981" header="0.31496062992125984" footer="0.31496062992125984"/>
+  <pageSetup paperSize="9" scale="75" fitToWidth="0" fitToHeight="0" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>